--- a/cet4/result/16_重生商女_千亿前妻不好惹/16_重生商女_千亿前妻不好惹_学习版.xlsx
+++ b/cet4/result/16_重生商女_千亿前妻不好惹/16_重生商女_千亿前妻不好惹_学习版.xlsx
@@ -397,787 +397,703 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D55"/>
+  <dimension ref="A1:D49"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>night</v>
       </c>
       <c r="B2" t="str">
-        <v>night</v>
+        <v>/naɪt/</v>
       </c>
       <c r="C2" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D2" t="str">
         <v>夜晚</v>
       </c>
-      <c r="D2" t="str">
-        <v>night(夜晚)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>sky</v>
       </c>
       <c r="B3" t="str">
-        <v>sky</v>
+        <v>/skaɪ/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D3" t="str">
         <v>天空</v>
       </c>
-      <c r="D3" t="str">
-        <v>sky(天空)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>ideal</v>
       </c>
       <c r="B4" t="str">
-        <v>ideal</v>
+        <v>/aɪˈdiːəl/</v>
       </c>
       <c r="C4" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D4" t="str">
         <v>理想的</v>
       </c>
-      <c r="D4" t="str">
-        <v>ideal(理想的)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>previously</v>
       </c>
       <c r="B5" t="str">
-        <v>previously</v>
+        <v>/ˈpriːviəsli/</v>
       </c>
       <c r="C5" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>以前</v>
       </c>
-      <c r="D5" t="str">
-        <v>previously(以前)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>agree</v>
       </c>
       <c r="B6" t="str">
-        <v>agree</v>
+        <v>/əˈɡriː/</v>
       </c>
       <c r="C6" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>同意</v>
       </c>
-      <c r="D6" t="str">
-        <v>agree(同意)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>prayer</v>
       </c>
       <c r="B7" t="str">
-        <v>prayer</v>
+        <v>/prer/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>祈祷</v>
       </c>
-      <c r="D7" t="str">
-        <v>prayer(祈祷)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>asleep</v>
       </c>
       <c r="B8" t="str">
-        <v>asleep</v>
+        <v>/əˈsliːp/</v>
       </c>
       <c r="C8" t="str">
+        <v>v./adj./adv.</v>
+      </c>
+      <c r="D8" t="str">
         <v>睡着的</v>
       </c>
-      <c r="D8" t="str">
-        <v>asleep(睡着的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>gasp</v>
       </c>
       <c r="B9" t="str">
-        <v>gasp</v>
+        <v>/ɡæsp/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>喘气</v>
       </c>
-      <c r="D9" t="str">
-        <v>gasp(喘气)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>moment</v>
       </c>
       <c r="B10" t="str">
-        <v>moment</v>
+        <v>/ˈmoʊmənt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>时刻</v>
       </c>
-      <c r="D10" t="str">
-        <v>moment(时刻)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>badly</v>
       </c>
       <c r="B11" t="str">
-        <v>badly</v>
+        <v>/ˈbædli/</v>
       </c>
       <c r="C11" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D11" t="str">
         <v>严重地</v>
       </c>
-      <c r="D11" t="str">
-        <v>badly(严重地)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>resign</v>
       </c>
       <c r="B12" t="str">
-        <v>resign</v>
+        <v>/rɪˈzaɪn/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>辞职</v>
       </c>
-      <c r="D12" t="str">
-        <v>resign(辞职)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>yourself</v>
       </c>
       <c r="B13" t="str">
-        <v>yourself</v>
+        <v>/jɔːˈself/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./pron.</v>
+      </c>
+      <c r="D13" t="str">
         <v>你自己</v>
       </c>
-      <c r="D13" t="str">
-        <v>yourself(你自己)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>stern</v>
       </c>
       <c r="B14" t="str">
-        <v>stern</v>
+        <v>/stɜːrn/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>严厉的</v>
       </c>
-      <c r="D14" t="str">
-        <v>stern(严厉的)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>waiter</v>
       </c>
       <c r="B15" t="str">
-        <v>waiter</v>
+        <v>/ˈweɪtər/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>服务员</v>
       </c>
-      <c r="D15" t="str">
-        <v>waiter(服务员)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>tea</v>
       </c>
       <c r="B16" t="str">
-        <v>tea</v>
+        <v>/tiː/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D16" t="str">
         <v>茶</v>
       </c>
-      <c r="D16" t="str">
-        <v>tea(茶)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>importance</v>
       </c>
       <c r="B17" t="str">
-        <v>importance</v>
+        <v>/ɪmˈpɔːrtns/</v>
       </c>
       <c r="C17" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D17" t="str">
         <v>重要性</v>
       </c>
-      <c r="D17" t="str">
-        <v>importance(重要性)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>document</v>
       </c>
       <c r="B18" t="str">
-        <v>document</v>
+        <v>/ˈdɑːkjumənt/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D18" t="str">
         <v>文件</v>
       </c>
-      <c r="D18" t="str">
-        <v>document(文件)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>policy</v>
       </c>
       <c r="B19" t="str">
-        <v>policy</v>
+        <v>/ˈpɑːləsi/</v>
       </c>
       <c r="C19" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D19" t="str">
         <v>政策</v>
       </c>
-      <c r="D19" t="str">
-        <v>policy(政策)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>amplify</v>
       </c>
       <c r="B20" t="str">
-        <v>amplify</v>
+        <v>/ˈæmplɪfaɪ/</v>
       </c>
       <c r="C20" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D20" t="str">
         <v>放大</v>
       </c>
-      <c r="D20" t="str">
-        <v>amplify(放大)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>helpful</v>
       </c>
       <c r="B21" t="str">
-        <v>helpful</v>
+        <v>/ˈhelpfl/</v>
       </c>
       <c r="C21" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D21" t="str">
         <v>有帮助的</v>
       </c>
-      <c r="D21" t="str">
-        <v>helpful(有帮助的)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>attitude</v>
       </c>
       <c r="B22" t="str">
-        <v>attitude</v>
+        <v>/ˈætɪtuːd/</v>
       </c>
       <c r="C22" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D22" t="str">
         <v>态度</v>
       </c>
-      <c r="D22" t="str">
-        <v>attitude(态度)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>regularly</v>
       </c>
       <c r="B23" t="str">
-        <v>regularly</v>
+        <v>/ˈreɡjələrli/</v>
       </c>
       <c r="C23" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D23" t="str">
         <v>定期地</v>
       </c>
-      <c r="D23" t="str">
-        <v>regularly(定期地)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>place</v>
       </c>
       <c r="B24" t="str">
-        <v>place</v>
+        <v>/pleɪs/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D24" t="str">
         <v>放置</v>
       </c>
-      <c r="D24" t="str">
-        <v>place(放置)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>assistant</v>
       </c>
       <c r="B25" t="str">
-        <v>assistant</v>
+        <v>/əˈsɪstənt/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D25" t="str">
         <v>助手</v>
       </c>
-      <c r="D25" t="str">
-        <v>assistant(助手)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>difficult</v>
       </c>
       <c r="B26" t="str">
-        <v>helpful</v>
+        <v>/ˈdɪfɪkəlt/</v>
       </c>
       <c r="C26" t="str">
-        <v>有帮助的</v>
+        <v>adj.</v>
       </c>
       <c r="D26" t="str">
-        <v>helpful(有帮助的)📢</v>
+        <v>困难的</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>beast</v>
       </c>
       <c r="B27" t="str">
-        <v>difficult</v>
+        <v>/biːst/</v>
       </c>
       <c r="C27" t="str">
-        <v>困难的</v>
+        <v>n.</v>
       </c>
       <c r="D27" t="str">
-        <v>difficult(困难的)📢</v>
+        <v>野兽</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>during</v>
       </c>
       <c r="B28" t="str">
-        <v>beast</v>
+        <v>/ˈdʊrɪŋ/</v>
       </c>
       <c r="C28" t="str">
-        <v>野兽</v>
+        <v>n./prep.</v>
       </c>
       <c r="D28" t="str">
-        <v>beast(野兽)📢</v>
+        <v>在...期间</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>accustomed</v>
       </c>
       <c r="B29" t="str">
-        <v>during</v>
+        <v>/əˈkʌstəmd/</v>
       </c>
       <c r="C29" t="str">
-        <v>在...期间</v>
+        <v>v./adj.</v>
       </c>
       <c r="D29" t="str">
-        <v>during(在...期间)📢</v>
+        <v>习惯的</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>generate</v>
       </c>
       <c r="B30" t="str">
-        <v>accustomed</v>
+        <v>/ˈdʒenəreɪt/</v>
       </c>
       <c r="C30" t="str">
-        <v>习惯的</v>
+        <v>vt.</v>
       </c>
       <c r="D30" t="str">
-        <v>accustomed(习惯的)📢</v>
+        <v>产生</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>group</v>
       </c>
       <c r="B31" t="str">
-        <v>generate</v>
+        <v>/ɡruːp/</v>
       </c>
       <c r="C31" t="str">
-        <v>产生</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D31" t="str">
-        <v>generate(产生)📢</v>
+        <v>组</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>sly</v>
       </c>
       <c r="B32" t="str">
-        <v>group</v>
+        <v>/slaɪ/</v>
       </c>
       <c r="C32" t="str">
-        <v>组</v>
+        <v>n./adj.</v>
       </c>
       <c r="D32" t="str">
-        <v>group(组)📢</v>
+        <v>狡猾的</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>evil</v>
       </c>
       <c r="B33" t="str">
-        <v>ideal</v>
+        <v>/ˈiːvl,ˈiːvɪl/</v>
       </c>
       <c r="C33" t="str">
-        <v>理想</v>
+        <v>n./adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>ideal(理想)📢</v>
+        <v>邪恶的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>competition</v>
       </c>
       <c r="B34" t="str">
-        <v>sly</v>
+        <v>/ˌkɑːmpəˈtɪʃn/</v>
       </c>
       <c r="C34" t="str">
-        <v>狡猾的</v>
+        <v>n.</v>
       </c>
       <c r="D34" t="str">
-        <v>sly(狡猾的)📢</v>
+        <v>竞争</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>restrain</v>
       </c>
       <c r="B35" t="str">
-        <v>evil</v>
+        <v>/rɪˈstreɪn/</v>
       </c>
       <c r="C35" t="str">
-        <v>邪恶的</v>
+        <v>vt.</v>
       </c>
       <c r="D35" t="str">
-        <v>evil(邪恶的)📢</v>
+        <v>抑制</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>ridge</v>
       </c>
       <c r="B36" t="str">
-        <v>competition</v>
+        <v>/rɪdʒ/</v>
       </c>
       <c r="C36" t="str">
-        <v>竞争</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>competition(竞争)📢</v>
+        <v>山脊</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>provide</v>
       </c>
       <c r="B37" t="str">
-        <v>restrain</v>
+        <v>/prəˈvaɪd/</v>
       </c>
       <c r="C37" t="str">
-        <v>抑制</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>restrain(抑制)📢</v>
+        <v>提供</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>transformer</v>
       </c>
       <c r="B38" t="str">
-        <v>ridge</v>
+        <v>/trænsˈfɔːrmər/</v>
       </c>
       <c r="C38" t="str">
-        <v>山脊</v>
+        <v>n.</v>
       </c>
       <c r="D38" t="str">
-        <v>ridge(山脊)📢</v>
+        <v>变压器</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>plenty</v>
       </c>
       <c r="B39" t="str">
-        <v>provide</v>
+        <v>/ˈplenti/</v>
       </c>
       <c r="C39" t="str">
-        <v>提供</v>
+        <v>n./v./adj./adv./pron.</v>
       </c>
       <c r="D39" t="str">
-        <v>provide(提供)📢</v>
+        <v>大量</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>kilogram</v>
       </c>
       <c r="B40" t="str">
-        <v>transformer</v>
+        <v>/ˈkɪləɡræm/</v>
       </c>
       <c r="C40" t="str">
-        <v>变压器</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>transformer(变压器)📢</v>
+        <v>公斤</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>consequence</v>
       </c>
       <c r="B41" t="str">
-        <v>plenty</v>
+        <v>/ˈkɑːnsɪkwens/</v>
       </c>
       <c r="C41" t="str">
-        <v>大量</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>plenty(大量)📢</v>
+        <v>结果</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>kid</v>
       </c>
       <c r="B42" t="str">
-        <v>kilogram</v>
+        <v>/kɪd/</v>
       </c>
       <c r="C42" t="str">
-        <v>公斤</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D42" t="str">
-        <v>kilogram(公斤)📢</v>
+        <v>小孩</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>sport</v>
       </c>
       <c r="B43" t="str">
-        <v>consequence</v>
+        <v>/spɔːrt/</v>
       </c>
       <c r="C43" t="str">
-        <v>结果</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>consequence(结果)📢</v>
+        <v>运动</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>entrance</v>
       </c>
       <c r="B44" t="str">
-        <v>evil</v>
+        <v>/ɪnˈtrɑ:ns;ˈentrəns/</v>
       </c>
       <c r="C44" t="str">
-        <v>邪恶的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D44" t="str">
-        <v>evil(邪恶的)📢</v>
+        <v>入口</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>bolt</v>
       </c>
       <c r="B45" t="str">
-        <v>kid</v>
+        <v>/boʊlt/</v>
       </c>
       <c r="C45" t="str">
-        <v>小孩</v>
+        <v>n./v.</v>
       </c>
       <c r="D45" t="str">
-        <v>kid(小孩)📢</v>
+        <v>闪电</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>maximum</v>
       </c>
       <c r="B46" t="str">
-        <v>sport</v>
+        <v>/ˈmæksɪməm/</v>
       </c>
       <c r="C46" t="str">
-        <v>运动</v>
+        <v>n./adj.</v>
       </c>
       <c r="D46" t="str">
-        <v>sport(运动)📢</v>
+        <v>最大</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>brief</v>
       </c>
       <c r="B47" t="str">
-        <v>entrance</v>
+        <v>/briːf/</v>
       </c>
       <c r="C47" t="str">
-        <v>入口</v>
+        <v>n./vt./adj.</v>
       </c>
       <c r="D47" t="str">
-        <v>entrance(入口)📢</v>
+        <v>简短的</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>guest</v>
       </c>
       <c r="B48" t="str">
-        <v>bolt</v>
+        <v>/ɡest/</v>
       </c>
       <c r="C48" t="str">
-        <v>闪电</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D48" t="str">
-        <v>bolt(闪电)📢</v>
+        <v>客人</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>terrific</v>
       </c>
       <c r="B49" t="str">
-        <v>competition</v>
+        <v>/təˈrɪfɪk/</v>
       </c>
       <c r="C49" t="str">
-        <v>竞争</v>
+        <v>adj.</v>
       </c>
       <c r="D49" t="str">
-        <v>competition(竞争)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>maximum</v>
-      </c>
-      <c r="C50" t="str">
-        <v>最大</v>
-      </c>
-      <c r="D50" t="str">
-        <v>maximum(最大)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>brief</v>
-      </c>
-      <c r="C51" t="str">
-        <v>简短的</v>
-      </c>
-      <c r="D51" t="str">
-        <v>brief(简短的)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>ideal</v>
-      </c>
-      <c r="C52" t="str">
-        <v>理想</v>
-      </c>
-      <c r="D52" t="str">
-        <v>ideal(理想)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>guest</v>
-      </c>
-      <c r="C53" t="str">
-        <v>客人</v>
-      </c>
-      <c r="D53" t="str">
-        <v>guest(客人)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>terrific</v>
-      </c>
-      <c r="C54" t="str">
         <v>极好的</v>
-      </c>
-      <c r="D54" t="str">
-        <v>terrific(极好的)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>sky</v>
-      </c>
-      <c r="C55" t="str">
-        <v>天空</v>
-      </c>
-      <c r="D55" t="str">
-        <v>sky(天空)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D55"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D49"/>
   </ignoredErrors>
 </worksheet>
 </file>